--- a/important_mails_2026-04-06.xlsx
+++ b/important_mails_2026-04-06.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H135"/>
+  <dimension ref="A1:H138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,21 +500,168 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Mon, 06 Apr 2026 01:10:45 +0000</t>
+          <t>Mon, 6 Apr 2026 15:00:18 +0000</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
+          <t>donotreply@amazon.com</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Re: 🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
+          <t>Je Factuur Verkoper Amazon.com.be voor 3/2026 (Votre Facture
+ Vendeur Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
+We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
+Als je toegang wilt krijgen tot je factuur, ga je naar je Seller Central-account &gt; Overzichten &gt; Bibliotheek met belastingdocumenten &gt; Belastingfacturen voor kosten verkoper.
+In je Seller Central-account kun je je factuur bekijken, downloaden of afdrukken.
+Als je nog vragen hebt, kun je contact opnemen met de Ondersteuning voor verkopers.
+Met vriendelijke groeten,
+Amazon.com.be
+ Monsieur/Madame Shen zhen shi wei hai zhong xin ke ji you xian,
+Nous vous écrivons pour vous informer que votre Facture Vendeur pour le mois de 3/2026 est maintenant disponible dans votre compte Seller Central.
+Pour accéder à votre facture, rendez-vous sur votre compte Seller Central et veuillez accéder à la page Rapports &gt; Bibliothèque d'informations fiscales &gt; Factures des frais du vendeur.
+Dans votre compte Seller Central, vous pourrez afficher, télécharger ou imprimer votre facture.
+Pour toute question, contactez le Support Vendeur.
+Cordialement,
+Amazon.com.be</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 6 Apr 2026 14:50:20 +0000</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 3.2026</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
+Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
+Navigieren Sie in Ihrem Seller Central-Konto zu Berichte &gt; Steuerdokumente &gt; Rechnungen über Verkaufsgebühren, um auf Ihr Dokument (Rechnung) zuzugreifen.
+In Ihrem Seller Central-Konto können Sie Ihr Dokument (Rechnung) anzeigen, herunterladen oder ausdrucken.
+Wenden Sie sich bei weiteren Fragen bitte an die Verkäuferhilfe.
+Freundliche Grüße,
+Amazon.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 6 Apr 2026 14:43:40 +0000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon.sa Merchant Invoice for 3/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 3/2026)</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
+We are writing to inform you that your electronic Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
+To access your invoice, go to your Seller Central Account &gt; Reports &gt; Tax Document Library &gt; Seller Fee Tax Invoices.
+In your Seller Central account, you will be able to view, download or print your invoice.
+If you have any questions, please contact Seller Support.
+Best regards,
+Amazon.sa
+ عزيزي Shen zhen shi wei hai zhong xin ke ji you xian،
+نراسلك لإبلاغك بأن فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاص بك لشهر 3/2026 متاح الآن في حساب Seller Central الخاص بك.
+للوصول إلى فاتورة الخاص بك، انتقل إلى حساب Seller Central الخاص بك &gt; التقارير &gt; مكتبة المستندات الضريبية &gt; فواتير ضريبة رسم البائع.
+في حساب Seller Central الخاص بك، ستتمكن من عرض {documentType}$ الخاص بك أو تنزيله أو طباعته.
+إذا كانت لديك أي أسئلة، فالمرجو التواصل مع دعم البائع.
+ مع أطيب التحيات،
+Amazon.sa</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 06 Apr 2026 01:10:45 +0000</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Re: 🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 I wanted to briefly follow up regarding the Vergleich.org award for your
@@ -546,39 +693,39 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:11:54 +0000</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (pVfzD86piw)</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -604,39 +751,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 06:25:09 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (CQhO1/+c38)</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -656,39 +803,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 13:38:25 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -708,39 +855,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 15:38:29 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -757,39 +904,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 12:51:47 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Eco-contribution and EPR Pay on Behalf service fee charges</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  96
@@ -812,91 +959,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 30 Mar 2026 15:13:23 +0000</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Your payment is on the way</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Congratulations! Your payment is on the way and will arrive soon.
- Disbursement Attempted
-Congratulations Weihai EU! Your payment is on the way and will arrive within three to five days.
-On 03/30/26 15:13 CEST, we initiated a transfer to your payment method (bank account ending in 229) in the amount of €
- 133.79.
- If the amount is less than expected, here are a few questions to consider:
- Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims, or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
- Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees, and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
-To learn more about Payment Reports in Seller Central, please visit our official course.
-We wish you continued success!
-Thank you for selling in the Amazon store,
-Amazon Services
-Help us improve your payment experience on Ama</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 04:56:03 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>【请勿回复】
 尊敬的销售合作伙伴，
@@ -919,39 +1014,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:19:17 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -969,39 +1064,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:18:50 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1019,39 +1114,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 21:25:34 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -1071,39 +1166,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 15:20:39 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12317833332] 其他账户问题</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家/供应商：您好！
 关于您 ASIN B0CSGBZG8W 购物车的问题，经过审核，我们发现该商品的价格不符合成为推荐商品的条件，因为它似乎过高。
@@ -1130,39 +1225,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 09:59:13 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>&lt;p&gt;Grazie per aver creato un nuovo caso: -- 12317833332&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>La ringraziamo per aver contattato il Supporto al venditore di Amazon.
 Abbiamo aperto un caso riguardo al suo problema. Un membro del nostro team la contatterà appena possibile. Rispondiamo alla maggior parte delle e-mail entro 12 ore.
@@ -1174,39 +1269,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 14:57:25 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Recargo relacionado con combustible y gastos de logística: Logística de Amazon y Logística Multicanal en la UE</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
  A partir del 17 de abril de 2026, se aplicará un recargo por combustible y gastos de logística del 1,5 % a las tarifas de gestión logística de Logística de Amazon. En el caso de Logística Multicanal, este recargo entrará en vigor el 2 de mayo de 2026.
@@ -1216,39 +1311,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 14:01:37 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Dopłata z tytułu kosztów paliwa i logistyki: usługi FBA i MFC w UE</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>96
  Od 17 kwietnia 2026 r. do opłat za realizację w programie „Realizacja przez Amazon” (FBA) zaczynamy doliczać dopłatę w wysokości 1,5% z tytułu kosztów paliwa i logistyki. W przypadku usługi „Realizacja wielokanałowa” (MCF) dopłata ta będzie miała zastosowanie od 2 maja 2026 r.
@@ -1258,39 +1353,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Wed, 01 Apr 2026 07:28:21 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 My name is Justin and I am writing to you from Berlin on behalf of
@@ -1320,39 +1415,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 03:11:45 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 03/2026</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -1370,39 +1465,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:25:14 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>规划您的亚马逊科技周促销活动</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -1419,39 +1514,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 15:17:53 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -1467,39 +1562,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 18:08:20 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para abril</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para abril
@@ -1528,92 +1623,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>其他风险类</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 30 Mar 2026 15:23:46 +0000</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Dein Einkaufswagen wartet</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
-Feuerfeste Unterlage, 130 × 80cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Grill Matte für Gasgrill Holzkohlegrill
- 18,45 €
-https://www.amazon.de/gp/product/B0DRC8LPGS/?ref_=
-Einkaufswagen anzeigen
-https://www.amazon.de/gp/cart/view.html?ref_=cor
-Schaue dir weitere Optionen an
-WOCVRYY130x160cm BBQ-Bodenschutzmatte Feuerschalenmatte Gasgrillmatte Unter Fireproof Underlay Wiederverwendbar,Antihaft-Material,Anti-Fall,Leicht zu reinigen und wasserdicht
- 22,99 €
-https://www.amazon.de/gp/product/B0CQNQ2YY3/?ref_=ci_mcx_mr_2p_0_lm
-Alckijy Feuerfeste Unterlage | 100 * 150cm Faltbare Hitzeschutzmatte | Bodenschutzmatte | Grillmatten | Bodenmatte | Grillteppich | Funkenschutzplatte | für BBQ Grills Kaminöfen Boden Rasen usw
- 20,15 €
-https://www.amazon.de/gp/product/B0CSGBZG8W/?ref_=ci_mcx_mr_2p_1_lm
-Weber Grillmatte - Klein (120 x 80cm), schützt Terasse/Balkon vor Fettspritzern oder tropfenden Flüssigkeiten, hitze- &amp;amp; witterungsbeständiges antibakteriellles Material, für alle Grills (17897)
- -19 % 25,20 € UVP: 31,08 €
-https://www.amazon.de/gp/product/B07ZCJHJQK/</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Apr 2026 09:46:59 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>C2S2 RXO Partner Broker fees increasing in May 2026</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -1631,39 +1673,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:16:39 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -1693,40 +1735,40 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 16:14:53 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.65 in an attempt to settle your Amazon.ca seller account balance.
@@ -1742,39 +1784,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 10:55:21 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (kpCypnMqWe)</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1794,39 +1836,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:27:53 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (UvRxALtvwM)</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -1852,39 +1894,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 03:56:37 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -1900,39 +1942,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 14:27:38 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -1953,39 +1995,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Mon, 16 Mar 2026 16:28:57 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF
 Dear Weihai US,
@@ -1999,40 +2041,40 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 16:15:06 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.03 in an attempt to settle your Amazon.ca seller account balance.
@@ -2048,39 +2090,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 17:16:41 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (V8b2nNxJ7Y)</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2100,39 +2142,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 16:36:35 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF
 Dear Weihai US,
@@ -2146,39 +2188,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 16:33:48 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (FVSl6sGweZ)</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2198,39 +2240,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:16:27 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2251,39 +2293,91 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 30 Mar 2026 15:13:23 +0000</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Your payment is on the way</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Congratulations! Your payment is on the way and will arrive soon.
+ Disbursement Attempted
+Congratulations Weihai EU! Your payment is on the way and will arrive within three to five days.
+On 03/30/26 15:13 CEST, we initiated a transfer to your payment method (bank account ending in 229) in the amount of €
+ 133.79.
+ If the amount is less than expected, here are a few questions to consider:
+ Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims, or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
+ Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees, and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
+To learn more about Payment Reports in Seller Central, please visit our official course.
+We wish you continued success!
+Thank you for selling in the Amazon store,
+Amazon Services
+Help us improve your payment experience on Ama</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:33:22 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -2300,39 +2394,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:38:31 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2349,39 +2443,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 14:28:40 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 207.96 in an attempt to settle your account balance.
@@ -2396,39 +2490,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Wed, 11 Mar 2026 15:11:44 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Ajustement du solde négatif sur l'ensemble de vos comptes</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2452,39 +2546,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 15:16:36 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 30.46. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -2498,39 +2592,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 14:57:34 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Negatieve saldoaanpassing voor al je accounts</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2547,39 +2641,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 13:38:27 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2599,39 +2693,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 07:07:52 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -2649,39 +2743,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 13:21:45 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -2699,39 +2793,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 13:01:16 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -2749,39 +2843,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 14:37:14 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Live Q&amp;A on customer feedback with experienced sellers</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ref--spc-em-na-frm-20260324/7z2bw3r/6577485148/h/BOm7kDreq_ieAJ8P9nkJWZ402nkYiTu_wgkPAn3aZYs)
 Connect with sellers experienced in customer feedback
@@ -2796,39 +2890,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:18:53 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -2846,39 +2940,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:13:28 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -2896,39 +2990,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:51:52 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -2946,39 +3040,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 08:16:10 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -2993,39 +3087,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 15:17:29 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -3040,39 +3134,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 14:28:08 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -3087,39 +3181,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 04:25:09 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -3138,40 +3232,40 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 11:52:08 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Submit UK import details by 21/05/2026 to avoid shipping
  restrictions</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>96
  Submit UK import details by 21/05/2026 to avoid shipping restrictions
@@ -3190,39 +3284,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 07:21:52 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility 96
  Complete Pan EU enrollment: Add NL products now
@@ -3232,39 +3326,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 21:58:00 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3282,39 +3376,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 21:10:27 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are contacting you to let you know that you could be missing out on sales opportunities because of your incomplete listings.
@@ -3330,39 +3424,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Sat, 14 Mar 2026 17:19:26 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -3381,39 +3475,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 12:08:48 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3431,39 +3525,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 09:36:41 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>"pc-eu-sesu-seller-compliance@amazon.com" &lt;pc-eu-sesu-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 11569978862] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您部分在【欧洲】各站点的部分【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】。
@@ -3485,39 +3579,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 21:37:56 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>"pc-us--sesu-cn-central-compliance@amazon.com" &lt;pc-us--sesu-cn-central-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 18425733131] 【需立即行动】请通过亚马逊认可的TIC服务提供商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您部分在【美国】的【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】。
@@ -3540,39 +3634,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:20 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -3591,39 +3685,92 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 30 Mar 2026 15:23:46 +0000</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>Dein Einkaufswagen wartet</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
+Feuerfeste Unterlage, 130 × 80cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Grill Matte für Gasgrill Holzkohlegrill
+ 18,45 €
+https://www.amazon.de/gp/product/B0DRC8LPGS/?ref_=
+Einkaufswagen anzeigen
+https://www.amazon.de/gp/cart/view.html?ref_=cor
+Schaue dir weitere Optionen an
+WOCVRYY130x160cm BBQ-Bodenschutzmatte Feuerschalenmatte Gasgrillmatte Unter Fireproof Underlay Wiederverwendbar,Antihaft-Material,Anti-Fall,Leicht zu reinigen und wasserdicht
+ 22,99 €
+https://www.amazon.de/gp/product/B0CQNQ2YY3/?ref_=ci_mcx_mr_2p_0_lm
+Alckijy Feuerfeste Unterlage | 100 * 150cm Faltbare Hitzeschutzmatte | Bodenschutzmatte | Grillmatten | Bodenmatte | Grillteppich | Funkenschutzplatte | für BBQ Grills Kaminöfen Boden Rasen usw
+ 20,15 €
+https://www.amazon.de/gp/product/B0CSGBZG8W/?ref_=ci_mcx_mr_2p_1_lm
+Weber Grillmatte - Klein (120 x 80cm), schützt Terasse/Balkon vor Fettspritzern oder tropfenden Flüssigkeiten, hitze- &amp;amp; witterungsbeständiges antibakteriellles Material, für alle Grills (17897)
+ -19 % 25,20 € UVP: 31,08 €
+https://www.amazon.de/gp/product/B07ZCJHJQK/</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 15:19:12 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3638,39 +3785,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:18:58 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -3684,40 +3831,40 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:14:09 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -3733,39 +3880,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:14:05 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -3781,39 +3928,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:10:09 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -3829,39 +3976,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:23:28 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -3877,40 +4024,40 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:18:15 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -3926,39 +4073,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 11:10:19 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -3976,39 +4123,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:28:37 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Raport podatkowy dla Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
  Przesłaliśmy Twój kwartalny raport podatkowy chińskiemu urzędowi skarbowemu. Możesz teraz pobrać raport do wglądu.
@@ -4024,39 +4171,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 15:00:54 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4071,39 +4218,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 10:50:35 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长
 尊敬的卖家，
@@ -4118,39 +4265,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 06:57:58 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -4171,40 +4318,40 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:21:26 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Submit your Prime Day 2026 Deals on March 24, review updated fees
  and eligibility</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>96
  Get ready to make this Prime Day your best yet.
@@ -4219,39 +4366,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 06:28:27 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Alckijy Feuerfeste Unterlage | 100 * 150cm Faltbare Hitzeschutzmatte | Bodenschutzmatte | Grillmatten | Bodenmatte | Grillteppich | Funkenschutzplatte | für BBQ Grills Kaminöfen Boden Rasen usw
@@ -4272,39 +4419,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 06:12:01 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>【爆单预警】百亿流量即将开闸！现在备货，抢占流量C位</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 						我们注意到您在店铺中有上架教育、办公类商品，特此预告您将有机会参与即将到来的全球教育采购 “超级旺季”！
@@ -4337,39 +4484,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 16:40:09 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -4385,39 +4532,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:16:22 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -4433,39 +4580,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 10:25:38 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4483,39 +4630,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 09:02:06 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -4532,39 +4679,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Tue, 17 Mar 2026 05:46:24 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>A Amazon enviou os itens vendidos</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>96
  Processamos e enviamos seus pedidos do programa FBA - Logística da Amazon.
@@ -4588,39 +4735,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 14:55:03 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4635,39 +4782,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 11:03:39 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>[Toma medidas] Proporciona más información en un plazo de 45 días para evitar la desactivación de tu cuenta en virtud de los requisitos de registro a efectos fiscales en Europa</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hola, Weihai EU:
@@ -4683,39 +4830,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:19:31 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>[Wymagane działanie] Podaj dodatkowe informacje w ciągu 45 dni, aby zapobiec dezaktywacji konta z powodu niespełnienia europejskich wymagań dotyczących rejestracji jako podatnik VAT</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -4732,40 +4879,40 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:50:00 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>[Azione richiesta] Fornisci informazioni entro 45 giorni ed evita
  la disattivazione dell'account per via dei requisiti di registrazione IVA</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -4781,39 +4928,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 14:17:27 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace KSA &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>FBA removal fees will not apply in UAE and Saudi Arabia</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>96
 Amazon UAE
@@ -4833,39 +4980,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 11:10:46 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -4881,40 +5028,40 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Wed, 11 Mar 2026 12:18:47 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;store-news@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Swimming Training Belt, 2.5-7.5M Adjustable Swimming Resistance
  Bands is still in your basket</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.co.uk/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -4930,39 +5077,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 09:31:04 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>春季促销日 2026：最后提报您促销活动的机会</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -4979,39 +5126,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Mon, 9 Mar 2026 15:38:05 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 2/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5030,39 +5177,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Mon, 9 Mar 2026 11:10:45 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -5080,39 +5227,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Sat, 7 Mar 2026 01:02:00 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 2/2026</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Credit Note for the month of 2/2026 is now available in your Seller Central Account.
@@ -5124,39 +5271,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:28:03 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5168,39 +5315,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:16:57 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Je Creditnota Verkoper Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Creditnota Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5212,39 +5359,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:10:12 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5256,39 +5403,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 22:15:50 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5300,39 +5447,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 21:01:28 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Realizacja przez Amazon za 2 2026</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Realizacja przez Amazon za miesiąc 2 i rok 2026.
@@ -5344,39 +5491,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:56:07 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -5388,39 +5535,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:28:14 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5432,39 +5579,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:17:57 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -5482,39 +5629,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:17:26 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以避免商品被停售</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  尊敬的 Weihai EU：
@@ -5557,39 +5704,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:57 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -5606,40 +5753,40 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:27 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -5657,39 +5804,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:12:48 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -5707,39 +5854,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:07:18 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5751,39 +5898,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:02:17 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5795,39 +5942,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:02:06 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 2/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5846,39 +5993,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:35:00 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5890,39 +6037,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:32:44 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5934,39 +6081,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:24:20 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5978,39 +6125,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 18:55:05 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6022,39 +6169,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 18:24:37 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -6066,39 +6213,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:58:56 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -6110,39 +6257,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:48:50 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -6154,39 +6301,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:11:22 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6198,39 +6345,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:54:03 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -6242,40 +6389,40 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:44:53 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 2/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -6294,39 +6441,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:38:12 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -6338,40 +6485,40 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:28:10 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>La tua Fattura Elettronica Amazon Marketing Service Amazon.it per
  2/2026</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>Gentile Shen zhen shi wei hai zhong xin ke ji you xian,
 Ti informiamo che la tua Fattura Elettronica Amazon Marketing Service per il mese di 2/2026 è ora disponibile sul tuo account di Seller Central.
@@ -6383,39 +6530,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:09:11 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -6427,39 +6574,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 09:57:24 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-09</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -6480,39 +6627,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 09:55:39 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6535,39 +6682,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:45:50 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-02</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -6588,39 +6735,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:04:22 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6644,39 +6791,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 09:25:34 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6699,39 +6846,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 10:45:45 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6754,39 +6901,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 10:21:22 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-03-26</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -6808,39 +6955,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 18:36:24 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -6856,39 +7003,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Sun, 22 Mar 2026 03:22:21 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -6904,40 +7051,40 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:33:36 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>[Action Required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -6956,40 +7103,40 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:34:06 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>[Action required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7007,39 +7154,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 17:09:21 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Envie os documentos de conformidade do produto para evitar a remoção da oferta</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>96
  Envie os documentos de conformidade do produto para evitar a remoção da oferta
@@ -7053,39 +7200,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 12:07:27 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Atenda aos requisitos de conformidade em ofertas</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>96
 Ação necessária: Informações importantes sobre suas ofertas
@@ -7103,39 +7250,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 12:42:53 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.nl&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Wijziging in geschiktheid voor opties voor premiumverzending</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>96
 Wijziging in geschiktheid voor opties voor premiumverzending

--- a/important_mails_2026-04-06.xlsx
+++ b/important_mails_2026-04-06.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H138"/>
+  <dimension ref="A1:H127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -485,37 +485,902 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 6 Apr 2026 15:50:12 +0000</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Automated unfulfillable FBA inventory removal notification</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Hello Weihai US,
+The following automated unfulfillable FBA removal orders have been created based on your automated settings.
+ Removal order ID W4mGNrNTVu
+ You can view the removals on Removal Order Details in your seller account by using the Search tool.
+The next removal order will be created as scheduled on April 20, 2026 in accordance with your settings if you have unfulfillable inventory at that time.
+To make changes to the shipping address, frequency of your automated unfulfillable removals, or other settings, go to Automated unfulfillable removal settings in your seller account.
+ Thank you.
+The Fulfillment by Amazon team
+Please note: This email was sent from a notification-only address that cannot accept incoming email. Please do not reply to this email.
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferences visit: Notification Preferences
+ Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
+ Amazon.com, 410 Terry Avenue North, Seattle, WA 98109-5210
+ SPC-USAmazon-2146248899841341</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 6 Apr 2026 16:54:29 +0000</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Refunds for digital services fees related to the Canadian DST will
+ begin on April 15</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>96
+ We’ll refund digital services fees and the taxes on those fees related to the Canadian digital services tax that we had charged from September 1, 2024, through August 15, 2025.
+ Hello,
+ On August 15, 2025, we stopped collecting digital service fees after the Canadian government announced its intention to repeal the Digital Services Tax Act. The Canadian government repealed the Digital Services Tax Act on March 26, 2026.
+ As a result, we’ll refund digital services fees and the taxes on those fees related to the Canadian digital services tax that we had charged from September 1, 2024 through August 15, 2025. We’ll begin processing the refunds on April 15, 2026, and we’ll complete them by May 15, 2026. No action is required from you.
+ To view your refunds, which will include the digital service fees and the taxes on those fees, follow these steps:
+- Go to the Payments dashboard .
+- Click Transaction View .
+- Under Transaction type , select Other .
+- Set the date range from April 15 2026, to May 15 2026, and click Update .
+- Download the file and open it in Excel.
+- Filter the Product details column with Digital services fee adjustment and Taxes on digital services fee adjustment .</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 6 Apr 2026 23:40:40 +0000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 3.2026</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
+Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
+Navigieren Sie in Ihrem Seller Central-Konto zu Berichte &gt; Steuerdokumente &gt; Rechnungen über Verkaufsgebühren, um auf Ihr Dokument (Rechnungskorrektur) zuzugreifen.
+In Ihrem Seller Central-Konto können Sie Ihr Dokument (Rechnungskorrektur) anzeigen, herunterladen oder ausdrucken.
+Wenden Sie sich bei weiteren Fragen bitte an die Verkäuferhilfe.
+Freundliche Grüße,
+Amazon.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 6 Apr 2026 22:17:10 +0000</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
+Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
+Navigieren Sie in Ihrem Seller Central-Konto zu Berichte &gt; Steuerdokumente &gt; Rechnungen über Verkaufsgebühren, um auf Ihr Dokument (Rechnung) zuzugreifen.
+In Ihrem Seller Central-Konto können Sie Ihr Dokument (Rechnung) anzeigen, herunterladen oder ausdrucken.
+Wenden Sie sich bei weiteren Fragen bitte an die Verkäuferhilfe.
+Freundliche Grüße,
+Amazon.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 6 Apr 2026 22:08:24 +0000</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
+We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
+Als je toegang wilt krijgen tot je factuur, ga je naar je Seller Central-account &gt; Overzichten &gt; Bibliotheek met belastingdocumenten &gt; Belastingfacturen voor kosten verkoper.
+In je Seller Central-account kun je je factuur bekijken, downloaden of afdrukken.
+Als je nog vragen hebt, kun je contact opnemen met de Ondersteuning voor verkopers.
+Met vriendelijke groeten,
+Amazon.nl</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 6 Apr 2026 22:03:23 +0000</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 3/2026</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
+We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
+To access your invoice, go to your Seller Central Account &gt; Reports &gt; Tax Document Library &gt; Seller Fee Tax Invoices.
+In your Seller Central account, you will be able to view, download or print your invoice.
+If you have any questions, please contact Seller Support.
+Best regards,
+Amazon.co.uk</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 6 Apr 2026 21:18:12 +0000</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
+We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
+Als je toegang wilt krijgen tot je factuur, ga je naar je Seller Central-account &gt; Overzichten &gt; Bibliotheek met belastingdocumenten &gt; Belastingfacturen voor kosten verkoper.
+In je Seller Central-account kun je je factuur bekijken, downloaden of afdrukken.
+Als je nog vragen hebt, kun je contact opnemen met de Ondersteuning voor verkopers.
+Met vriendelijke groeten,
+Amazon.nl</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 6 Apr 2026 20:40:48 +0000</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Din Faktura Fraktas Av Amazon Amazon.se för 3/2026</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
+Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
+För att komma åt ditt fakturagår du till ditt Seller Central-konto &gt; Rapporter &gt; Bibliotek för skattedokument &gt; Skattefakturor för säljaravgifter.
+På ditt Seller Central-konto kan du se, ladda ner eller skriva ut ditt faktura.
+Om du har några frågor, kontakta säljarsupport.
+Vänliga hälsningar,
+Amazon.se</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 6 Apr 2026 20:23:05 +0000</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
+Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
+Navigieren Sie in Ihrem Seller Central-Konto zu Berichte &gt; Steuerdokumente &gt; Rechnungen über Verkaufsgebühren, um auf Ihr Dokument (Rechnung) zuzugreifen.
+In Ihrem Seller Central-Konto können Sie Ihr Dokument (Rechnung) anzeigen, herunterladen oder ausdrucken.
+Wenden Sie sich bei weiteren Fragen bitte an die Verkäuferhilfe.
+Freundliche Grüße,
+Amazon.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 6 Apr 2026 20:10:52 +0000</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 3/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 3/2026)</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
+We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
+Als je toegang wilt krijgen tot je factuur, ga je naar je Seller Central-account &gt; Overzichten &gt; Bibliotheek met belastingdocumenten &gt; Belastingfacturen voor kosten verkoper.
+In je Seller Central-account kun je je factuur bekijken, downloaden of afdrukken.
+Als je nog vragen hebt, kun je contact opnemen met de Ondersteuning voor verkopers.
+Met vriendelijke groeten,
+Amazon.com.be
+ Monsieur/Madame Shen zhen shi wei hai zhong xin ke ji you xian,
+Nous vous écrivons pour vous informer que votre Facture Expédié Par Amazon pour le mois de 3/2026 est maintenant disponible dans votre compte Seller Central.
+Pour accéder à votre facture, rendez-vous sur votre compte Seller Central et veuillez accéder à la page Rapports &gt; Bibliothèque d'informations fiscales &gt; Factures des frais du vendeur.
+Dans votre compte Seller Central, vous pourrez afficher, télécharger ou imprimer votre facture.
+Pour toute question, contactez le Support Vendeur.
+Cordialement,
+Amazon.com.be</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 6 Apr 2026 20:00:59 +0000</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 3.2026</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
+Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
+Navigieren Sie in Ihrem Seller Central-Konto zu Berichte &gt; Steuerdokumente &gt; Rechnungen über Verkaufsgebühren, um auf Ihr Dokument (Rechnung) zuzugreifen.
+In Ihrem Seller Central-Konto können Sie Ihr Dokument (Rechnung) anzeigen, herunterladen oder ausdrucken.
+Wenden Sie sich bei weiteren Fragen bitte an die Verkäuferhilfe.
+Freundliche Grüße,
+Amazon.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 6 Apr 2026 19:23:08 +0000</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 3.2026</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
+Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
+Navigieren Sie in Ihrem Seller Central-Konto zu Berichte &gt; Steuerdokumente &gt; Rechnungen über Verkaufsgebühren, um auf Ihr Dokument (Rechnung) zuzugreifen.
+In Ihrem Seller Central-Konto können Sie Ihr Dokument (Rechnung) anzeigen, herunterladen oder ausdrucken.
+Wenden Sie sich bei weiteren Fragen bitte an die Verkäuferhilfe.
+Freundliche Grüße,
+Amazon.de</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 6 Apr 2026 18:31:47 +0000</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 3/2026</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
+We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 3/2026 is now available in your Seller Central Account.
+To access your invoice, go to your Seller Central Account &gt; Reports &gt; Tax Document Library &gt; Seller Fee Tax Invoices.
+In your Seller Central account, you will be able to view, download or print your invoice.
+If you have any questions, please contact Seller Support.
+Best regards,
+Amazon.co.uk</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 6 Apr 2026 16:54:15 +0000</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Din Faktura Säljare Amazon.se för 3/2026</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
+Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
+För att komma åt ditt fakturagår du till ditt Seller Central-konto &gt; Rapporter &gt; Bibliotek för skattedokument &gt; Skattefakturor för säljaravgifter.
+På ditt Seller Central-konto kan du se, ladda ner eller skriva ut ditt faktura.
+Om du har några frågor, kontakta säljarsupport.
+Vänliga hälsningar,
+Amazon.se</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 6 Apr 2026 16:52:00 +0000</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Je Factuur Verkoper Amazon.nl voor 3/2026</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
+We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
+Als je toegang wilt krijgen tot je factuur, ga je naar je Seller Central-account &gt; Overzichten &gt; Bibliotheek met belastingdocumenten &gt; Belastingfacturen voor kosten verkoper.
+In je Seller Central-account kun je je factuur bekijken, downloaden of afdrukken.
+Als je nog vragen hebt, kun je contact opnemen met de Ondersteuning voor verkopers.
+Met vriendelijke groeten,
+Amazon.nl</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 6 Apr 2026 16:39:20 +0000</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon.co.uk Merchant Invoice for 3/2026</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
+We are writing to inform you that your electronic Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
+To access your invoice, go to your Seller Central Account &gt; Reports &gt; Tax Document Library &gt; Seller Fee Tax Invoices.
+In your Seller Central account, you will be able to view, download or print your invoice.
+If you have any questions, please contact Seller Support.
+Best regards,
+Amazon.co.uk</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 6 Apr 2026 16:07:04 +0000</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Din Faktura Fraktas Av Amazon Amazon.se för 3/2026</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
+Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 3/2026 nu finns tillgänglig på ditt Seller Central-konto.
+För att komma åt ditt fakturagår du till ditt Seller Central-konto &gt; Rapporter &gt; Bibliotek för skattedokument &gt; Skattefakturor för säljaravgifter.
+På ditt Seller Central-konto kan du se, ladda ner eller skriva ut ditt faktura.
+Om du har några frågor, kontakta säljarsupport.
+Vänliga hälsningar,
+Amazon.se</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 6 Apr 2026 16:06:30 +0000</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 3/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 3/2026)</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
+We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
+Als je toegang wilt krijgen tot je factuur, ga je naar je Seller Central-account &gt; Overzichten &gt; Bibliotheek met belastingdocumenten &gt; Belastingfacturen voor kosten verkoper.
+In je Seller Central-account kun je je factuur bekijken, downloaden of afdrukken.
+Als je nog vragen hebt, kun je contact opnemen met de Ondersteuning voor verkopers.
+Met vriendelijke groeten,
+Amazon.com.be
+ Monsieur/Madame Shen zhen shi wei hai zhong xin ke ji you xian,
+Nous vous écrivons pour vous informer que votre Facture Expédié Par Amazon pour le mois de 3/2026 est maintenant disponible dans votre compte Seller Central.
+Pour accéder à votre facture, rendez-vous sur votre compte Seller Central et veuillez accéder à la page Rapports &gt; Bibliothèque d'informations fiscales &gt; Factures des frais du vendeur.
+Dans votre compte Seller Central, vous pourrez afficher, télécharger ou imprimer votre facture.
+Pour toute question, contactez le Support Vendeur.
+Cordialement,
+Amazon.com.be</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 6 Apr 2026 15:55:59 +0000</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>donotreply@amazon.com</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 3/2026</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
+We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
+Als je toegang wilt krijgen tot je factuur, ga je naar je Seller Central-account &gt; Overzichten &gt; Bibliotheek met belastingdocumenten &gt; Belastingfacturen voor kosten verkoper.
+In je Seller Central-account kun je je factuur bekijken, downloaden of afdrukken.
+Als je nog vragen hebt, kun je contact opnemen met de Ondersteuning voor verkopers.
+Met vriendelijke groeten,
+Amazon.nl</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 15:00:18 +0000</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 3/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 3/2026)</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 3 2026 nu beschikbaar is in je Seller Central-account.
@@ -534,39 +1399,39 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 14:50:20 +0000</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 3.2026</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 3.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -578,39 +1443,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Mon, 6 Apr 2026 14:43:40 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Merchant Invoice for 3/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 3/2026)</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 3/2026 is now available in your Seller Central Account.
@@ -629,39 +1494,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Mon, 06 Apr 2026 01:10:45 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Re: 🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 I wanted to briefly follow up regarding the Vergleich.org award for your
@@ -693,39 +1558,84 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 6 Apr 2026 22:48:38 +0000</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Remove aged, stranded and unfulfillable inventory by April 30</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Take action now to avoid automatic removal of your Fulfilment by Amazon inventory.
+ Hello,
+ Starting from April 30, 2026, your Fulfilment by Amazon (FBA) inventory that’s been stored over 270 days (aged), stranded over 60 days or unfulfillable over 14 days will be removed from our UK and EU fulfilment centres to free up capacity in our network.
+ If you don’t complete one of the following actions by April 30, 2026, we may automatically dispose, donate, liquidate or return your inventory.
+- For aged inventory (270+ days): Review your at-risk inventory in FBA inventory , then go to Automated fulfillable settings in Seller Central settings and choose a removal option: Disable, return (processing may take up to 90 days) or dispose (liquidation is available for eligible inventory). If you choose Disable, we will not remove your aged inventory.
+- For unfulfillable inventory: Go to Remove unfulfillable inventory and create a removal order.
+- For stranded inventory: Go to Fix stranded inventory and create a removal order or select “Edit automatic action settings” to configure your removal preferences. Note: If you’ve created a return order for FBA inventory in last six months, we’ll att</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:11:54 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (pVfzD86piw)</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -751,39 +1661,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 06:25:09 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (CQhO1/+c38)</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -803,39 +1713,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 13:38:25 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -855,39 +1765,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 15:38:29 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -904,39 +1814,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 12:51:47 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Eco-contribution and EPR Pay on Behalf service fee charges</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  96
@@ -959,39 +1869,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 04:56:03 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>【请勿回复】
 尊敬的销售合作伙伴，
@@ -1014,39 +1924,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:19:17 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1064,39 +1974,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:18:50 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1114,39 +2024,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 21:25:34 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -1166,39 +2076,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 15:20:39 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12317833332] 其他账户问题</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家/供应商：您好！
 关于您 ASIN B0CSGBZG8W 购物车的问题，经过审核，我们发现该商品的价格不符合成为推荐商品的条件，因为它似乎过高。
@@ -1225,39 +2135,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Sun, 5 Apr 2026 09:59:13 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>&lt;p&gt;Grazie per aver creato un nuovo caso: -- 12317833332&lt;/p&gt;</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>La ringraziamo per aver contattato il Supporto al venditore di Amazon.
 Abbiamo aperto un caso riguardo al suo problema. Un membro del nostro team la contatterà appena possibile. Rispondiamo alla maggior parte delle e-mail entro 12 ore.
@@ -1269,39 +2179,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 14:57:25 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Recargo relacionado con combustible y gastos de logística: Logística de Amazon y Logística Multicanal en la UE</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>96
  A partir del 17 de abril de 2026, se aplicará un recargo por combustible y gastos de logística del 1,5 % a las tarifas de gestión logística de Logística de Amazon. En el caso de Logística Multicanal, este recargo entrará en vigor el 2 de mayo de 2026.
@@ -1311,39 +2221,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 14:01:37 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Dopłata z tytułu kosztów paliwa i logistyki: usługi FBA i MFC w UE</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>96
  Od 17 kwietnia 2026 r. do opłat za realizację w programie „Realizacja przez Amazon” (FBA) zaczynamy doliczać dopłatę w wysokości 1,5% z tytułu kosztów paliwa i logistyki. W przypadku usługi „Realizacja wielokanałowa” (MCF) dopłata ta będzie miała zastosowanie od 2 maja 2026 r.
@@ -1353,39 +2263,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Wed, 01 Apr 2026 07:28:21 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 My name is Justin and I am writing to you from Berlin on behalf of
@@ -1415,39 +2325,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 03:11:45 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 03/2026</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -1465,39 +2375,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:25:14 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>规划您的亚马逊科技周促销活动</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -1514,39 +2424,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 15:17:53 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -1562,100 +2472,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>其他风险类</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 30 Mar 2026 18:08:20 +0000</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Tus límites de capacidad de Logística de Amazon para abril</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>96
- Tus límites de capacidad de Logística de Amazon para abril
- Hola:
- Se confirmaron tus límites de capacidad para el próximo periodo.
- Pronóstico de capacidad para el periodo del abr. 1 al 30, a partir del mar. 28:
- Tipo de almacenamiento
- Límite de capacidad total (metros cúbicos)
- Tamaño estándar
- 16.42
- Tamaño grande
- 21.66
- Para ver tus límites más actualizados, así como los límites de capacidad estimados para los dos meses siguientes, ve a los envíos de Logística de Amazon .
- En la siguiente tabla, se muestra el uso de la capacidad de Logística de Amazon a partir del mar. 27.
- Tipo de almacenamiento
- Uso sin los envíos abiertos incluidos (metros cúbicos)
- Uso con los envíos abiertos incluidos (metros cúbicos)
- Tamaño estándar
- 0.00
- 0.00
- Tamaño grande
- 0.00
- 0.00
- Cómo se establecen los límites de capacidad de Logística de Amazon
- Tus límites de capacidad dependen de tu puntuación del índice de desempeño de inventario y otros factores, como las proyecciones de ventas para tus ASIN, la capacidad del centro de distribución y el plazo de entrega de los envíos. Las estimaciones variarán en función de los cambios en tu puntuación del índice de desempeño de inventario y pueden au</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Apr 2026 09:46:59 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>C2S2 RXO Partner Broker fees increasing in May 2026</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -1673,39 +2522,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:16:39 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -1735,40 +2584,40 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 16:14:53 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.65 in an attempt to settle your Amazon.ca seller account balance.
@@ -1784,39 +2633,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 10:55:21 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (kpCypnMqWe)</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1836,39 +2685,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:27:53 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (UvRxALtvwM)</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -1894,39 +2743,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 03:56:37 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -1942,39 +2791,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 14:27:38 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -1995,39 +2844,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Mon, 16 Mar 2026 16:28:57 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF
 Dear Weihai US,
@@ -2041,40 +2890,40 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 16:15:06 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.03 in an attempt to settle your Amazon.ca seller account balance.
@@ -2090,39 +2939,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 17:16:41 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (V8b2nNxJ7Y)</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2142,39 +2991,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 16:36:35 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF
 Dear Weihai US,
@@ -2188,39 +3037,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 16:33:48 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (FVSl6sGweZ)</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2240,92 +3089,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 6 Mar 2026 17:16:27 +0000</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Automated unfulfillable FBA inventory removal notification</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hello Weihai US,
-The following automated unfulfillable FBA removal orders have been created based on your automated settings.
- Removal order ID UvRxALtvwM
- You can view the removals on Removal Order Details in your seller account by using the Search tool.
-The next removal order will be created as scheduled on March 20, 2026 in accordance with your settings if you have unfulfillable inventory at that time.
-To make changes to the shipping address, frequency of your automated unfulfillable removals, or other settings, go to Automated unfulfillable removal settings in your seller account.
- Thank you.
-The Fulfillment by Amazon team
-Please note: This email was sent from a notification-only address that cannot accept incoming email. Please do not reply to this email.
- Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferences visit: Notification Preferences
- Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
- Amazon.com, 410 Terry Avenue North, Seattle, WA 98109-5210
- SPC-USAmazon-404622472692539</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 15:13:23 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2345,39 +3141,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:33:22 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -2394,39 +3190,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:38:31 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2443,39 +3239,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 14:28:40 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 207.96 in an attempt to settle your account balance.
@@ -2490,39 +3286,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Wed, 11 Mar 2026 15:11:44 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Ajustement du solde négatif sur l'ensemble de vos comptes</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2546,39 +3342,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 15:16:36 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 30.46. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -2592,39 +3388,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 14:57:34 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Negatieve saldoaanpassing voor al je accounts</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2641,39 +3437,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 13:38:27 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2693,39 +3489,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 07:07:52 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -2743,39 +3539,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 13:21:45 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -2793,39 +3589,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 13:01:16 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -2843,39 +3639,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 14:37:14 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Live Q&amp;A on customer feedback with experienced sellers</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ref--spc-em-na-frm-20260324/7z2bw3r/6577485148/h/BOm7kDreq_ieAJ8P9nkJWZ402nkYiTu_wgkPAn3aZYs)
 Connect with sellers experienced in customer feedback
@@ -2890,39 +3686,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:18:53 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -2940,39 +3736,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:13:28 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -2990,39 +3786,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:51:52 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3040,39 +3836,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 08:16:10 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -3087,39 +3883,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 15:17:29 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -3134,39 +3930,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 14:28:08 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -3181,39 +3977,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 04:25:09 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -3232,40 +4028,40 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 11:52:08 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Submit UK import details by 21/05/2026 to avoid shipping
  restrictions</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
  Submit UK import details by 21/05/2026 to avoid shipping restrictions
@@ -3284,39 +4080,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 07:21:52 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility 96
  Complete Pan EU enrollment: Add NL products now
@@ -3326,39 +4122,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 21:58:00 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3376,39 +4172,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 21:10:27 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are contacting you to let you know that you could be missing out on sales opportunities because of your incomplete listings.
@@ -3424,39 +4220,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Sat, 14 Mar 2026 17:19:26 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -3475,39 +4271,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 12:08:48 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3525,39 +4321,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 09:36:41 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>"pc-eu-sesu-seller-compliance@amazon.com" &lt;pc-eu-sesu-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 11569978862] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您部分在【欧洲】各站点的部分【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】。
@@ -3579,39 +4375,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 21:37:56 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>"pc-us--sesu-cn-central-compliance@amazon.com" &lt;pc-us--sesu-cn-central-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 18425733131] 【需立即行动】请通过亚马逊认可的TIC服务提供商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您部分在【美国】的【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】。
@@ -3634,90 +4430,100 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 6 Mar 2026 20:15:20 +0000</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to avoid listing deactivation</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 30 Mar 2026 18:08:20 +0000</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Tus límites de capacidad de Logística de Amazon para abril</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>96
- Hello Weihai EU,
- Some of your listings are at risk of deactivation due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject to these compliance requirements.
- For step-by-step instructions, see our Submit compliance documents or appeal a documentation request help page.
- To avoid further impact to your account, close or delete any non-compliant listings that you do</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+ Tus límites de capacidad de Logística de Amazon para abril
+ Hola:
+ Se confirmaron tus límites de capacidad para el próximo periodo.
+ Pronóstico de capacidad para el periodo del abr. 1 al 30, a partir del mar. 28:
+ Tipo de almacenamiento
+ Límite de capacidad total (metros cúbicos)
+ Tamaño estándar
+ 16.42
+ Tamaño grande
+ 21.66
+ Para ver tus límites más actualizados, así como los límites de capacidad estimados para los dos meses siguientes, ve a los envíos de Logística de Amazon .
+ En la siguiente tabla, se muestra el uso de la capacidad de Logística de Amazon a partir del mar. 27.
+ Tipo de almacenamiento
+ Uso sin los envíos abiertos incluidos (metros cúbicos)
+ Uso con los envíos abiertos incluidos (metros cúbicos)
+ Tamaño estándar
+ 0.00
+ 0.00
+ Tamaño grande
+ 0.00
+ 0.00
+ Cómo se establecen los límites de capacidad de Logística de Amazon
+ Tus límites de capacidad dependen de tu puntuación del índice de desempeño de inventario y otros factores, como las proyecciones de ventas para tus ASIN, la capacidad del centro de distribución y el plazo de entrega de los envíos. Las estimaciones variarán en función de los cambios en tu puntuación del índice de desempeño de inventario y pueden au</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 15:23:46 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 130 × 80cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Grill Matte für Gasgrill Holzkohlegrill
@@ -3738,39 +4544,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 15:19:12 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3785,39 +4591,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:18:58 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -3831,40 +4637,40 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:14:09 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -3880,39 +4686,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:14:05 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -3928,39 +4734,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:10:09 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -3976,39 +4782,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:23:28 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -4024,40 +4830,40 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:18:15 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -4073,39 +4879,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 11:10:19 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -4123,39 +4929,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:28:37 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Raport podatkowy dla Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>96
  Przesłaliśmy Twój kwartalny raport podatkowy chińskiemu urzędowi skarbowemu. Możesz teraz pobrać raport do wglądu.
@@ -4171,39 +4977,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 15:00:54 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4218,39 +5024,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 10:50:35 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长
 尊敬的卖家，
@@ -4265,39 +5071,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 06:57:58 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -4318,40 +5124,40 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:21:26 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Submit your Prime Day 2026 Deals on March 24, review updated fees
  and eligibility</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>96
  Get ready to make this Prime Day your best yet.
@@ -4366,39 +5172,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 06:28:27 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Alckijy Feuerfeste Unterlage | 100 * 150cm Faltbare Hitzeschutzmatte | Bodenschutzmatte | Grillmatten | Bodenmatte | Grillteppich | Funkenschutzplatte | für BBQ Grills Kaminöfen Boden Rasen usw
@@ -4419,39 +5225,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 06:12:01 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>【爆单预警】百亿流量即将开闸！现在备货，抢占流量C位</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 						我们注意到您在店铺中有上架教育、办公类商品，特此预告您将有机会参与即将到来的全球教育采购 “超级旺季”！
@@ -4484,39 +5290,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 16:40:09 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -4532,39 +5338,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:16:22 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -4580,39 +5386,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 10:25:38 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4630,39 +5436,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 09:02:06 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -4679,39 +5485,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Tue, 17 Mar 2026 05:46:24 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>A Amazon enviou os itens vendidos</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>96
  Processamos e enviamos seus pedidos do programa FBA - Logística da Amazon.
@@ -4735,39 +5541,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 14:55:03 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4782,39 +5588,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 11:03:39 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>[Toma medidas] Proporciona más información en un plazo de 45 días para evitar la desactivación de tu cuenta en virtud de los requisitos de registro a efectos fiscales en Europa</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hola, Weihai EU:
@@ -4830,39 +5636,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:19:31 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>[Wymagane działanie] Podaj dodatkowe informacje w ciągu 45 dni, aby zapobiec dezaktywacji konta z powodu niespełnienia europejskich wymagań dotyczących rejestracji jako podatnik VAT</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -4879,40 +5685,40 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:50:00 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>[Azione richiesta] Fornisci informazioni entro 45 giorni ed evita
  la disattivazione dell'account per via dei requisiti di registrazione IVA</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -4928,39 +5734,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 14:17:27 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace KSA &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>FBA removal fees will not apply in UAE and Saudi Arabia</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>96
 Amazon UAE
@@ -4980,39 +5786,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 11:10:46 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -5028,40 +5834,40 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Wed, 11 Mar 2026 12:18:47 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;store-news@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Swimming Training Belt, 2.5-7.5M Adjustable Swimming Resistance
  Bands is still in your basket</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.co.uk/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -5077,39 +5883,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 09:31:04 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>春季促销日 2026：最后提报您促销活动的机会</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -5126,39 +5932,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Mon, 9 Mar 2026 15:38:05 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 2/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5177,39 +5983,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Mon, 9 Mar 2026 11:10:45 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -5227,864 +6033,10 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 7 Mar 2026 01:02:00 +0000</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F96" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon.co.uk Merchant Credit Note for 2/2026</t>
-        </is>
-      </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
-We are writing to inform you that your electronic Merchant Credit Note for the month of 2/2026 is now available in your Seller Central Account.
-To access your credit note, go to your Seller Central Account &gt; Reports &gt; Tax Document Library &gt; Seller Fee Tax Invoices.
-In your Seller Central account, you will be able to view, download or print your credit note.
-If you have any questions, please contact Seller Support.
-Best regards,
-Amazon.co.uk</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 6 Mar 2026 23:28:03 +0000</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 2.2026</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
-Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
-Navigieren Sie in Ihrem Seller Central-Konto zu Berichte &gt; Steuerdokumente &gt; Rechnungen über Verkaufsgebühren, um auf Ihr Dokument (Rechnungskorrektur) zuzugreifen.
-In Ihrem Seller Central-Konto können Sie Ihr Dokument (Rechnungskorrektur) anzeigen, herunterladen oder ausdrucken.
-Wenden Sie sich bei weiteren Fragen bitte an die Verkäuferhilfe.
-Freundliche Grüße,
-Amazon.de</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 6 Mar 2026 23:16:57 +0000</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>Je Creditnota Verkoper Amazon.nl voor 2/2026</t>
-        </is>
-      </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
-We sturen je dit bericht om je te laten weten dat je elektronische Creditnota Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
-Als je toegang wilt krijgen tot je creditnota, ga je naar je Seller Central-account &gt; Overzichten &gt; Bibliotheek met belastingdocumenten &gt; Belastingfacturen voor kosten verkoper.
-In je Seller Central-account kun je je creditnota bekijken, downloaden of afdrukken.
-Als je nog vragen hebt, kun je contact opnemen met de Ondersteuning voor verkopers.
-Met vriendelijke groeten,
-Amazon.nl</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 6 Mar 2026 23:10:12 +0000</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 2.2026</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
-Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
-Navigieren Sie in Ihrem Seller Central-Konto zu Berichte &gt; Steuerdokumente &gt; Rechnungen über Verkaufsgebühren, um auf Ihr Dokument (Rechnungskorrektur) zuzugreifen.
-In Ihrem Seller Central-Konto können Sie Ihr Dokument (Rechnungskorrektur) anzeigen, herunterladen oder ausdrucken.
-Wenden Sie sich bei weiteren Fragen bitte an die Verkäuferhilfe.
-Freundliche Grüße,
-Amazon.de</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 6 Mar 2026 22:15:50 +0000</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
-        </is>
-      </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
-Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
-Navigieren Sie in Ihrem Seller Central-Konto zu Berichte &gt; Steuerdokumente &gt; Rechnungen über Verkaufsgebühren, um auf Ihr Dokument (Rechnung) zuzugreifen.
-In Ihrem Seller Central-Konto können Sie Ihr Dokument (Rechnung) anzeigen, herunterladen oder ausdrucken.
-Wenden Sie sich bei weiteren Fragen bitte an die Verkäuferhilfe.
-Freundliche Grüße,
-Amazon.de</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 6 Mar 2026 21:01:28 +0000</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>Amazon.pl – Faktura Realizacja przez Amazon za 2 2026</t>
-        </is>
-      </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
-Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Realizacja przez Amazon za miesiąc 2 i rok 2026.
-Aby uzyskać dostęp do tego dokumentu typu faktura, przejdź na konto Seller Central &gt; Raporty &gt; Dokumenty podatkowe &gt; Faktury podatkowe z tytułu opłat od sprzedawcy.
-Na koncie Seller Central możesz wyświetlić, pobrać i wydrukować taki dokument (faktura).
-Jeśli masz jakieś pytania, skontaktuj się z działem pomocy dla sprzedawców.
-Pozdrawiamy,
-Amazon.pl</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 6 Mar 2026 20:56:07 +0000</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>Din Faktura Fraktas Av Amazon Amazon.se för 2/2026</t>
-        </is>
-      </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
-Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
-För att komma åt ditt fakturagår du till ditt Seller Central-konto &gt; Rapporter &gt; Bibliotek för skattedokument &gt; Skattefakturor för säljaravgifter.
-På ditt Seller Central-konto kan du se, ladda ner eller skriva ut ditt faktura.
-Om du har några frågor, kontakta säljarsupport.
-Vänliga hälsningar,
-Amazon.se</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 6 Mar 2026 20:28:14 +0000</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon.ie Fulfillment by Amazon Merchant Invoice for 2/2026</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
-We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
-To access your invoice, go to your Seller Central Account &gt; Reports &gt; Tax Document Library &gt; Seller Fee Tax Invoices.
-In your Seller Central account, you will be able to view, download or print your invoice.
-If you have any questions, please contact Seller Support.
-Best regards,
-Amazon.ie</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 6 Mar 2026 20:17:57 +0000</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="inlineStr">
-        <is>
-          <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
-        </is>
-      </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hola, Weihai EU:
- Algunos de tus listings están en riesgo de desactivación debido a que tus productos no cumplen los requisitos obligatorios. Revisa a continuación los detalles y siguientes pasos. Los listings afectados aparecen al final de este correo electrónico.
- ¿A qué se debe esto?
- Tomamos esta medida porque a estos productos les falta información de cumplimiento normativo obligatoria. Para más información sobre las leyes, normativas y políticas de Amazon aplicables, consulta Cumplimiento y seguridad de los productos .
- En la tabla que aparece al final de este correo electrónico se proporcionan los requisitos de cumplimiento normativo específicos del producto.
- ¿Cómo puedo reactivar mis listings?
- Para proporcionar la información de cumplimiento normativo obligatoria, ve a la página Estado de la cuenta y localiza las solicitudes de cumplimiento normativo del producto:
--
- Si dispones de la documentación obligatoria, sigue las instrucciones para presentar los documentos de cumplimiento normativo.
--
- Si crees que tus productos están exentos de estos requisitos, presenta documentación que demuestre por qué no están sujetos a estos requisitos de cumplimiento normativo.
- Para v</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 6 Mar 2026 20:17:26 +0000</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>提交商品安全文件以避免商品被停售</t>
-        </is>
-      </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
- 尊敬的 Weihai EU：
-您好！
- 您的部分商品因缺少必要的商品合规信息而面临被停售的风险。查看下面的详细信息和后续步骤。受影响的商品显示在此电子邮件的末尾。
- 为什么会发生这种情况？
- 我们之所以采取此措施，是因为这些商品缺少必要的合规信息。请查看我们的 商品安全与合规 帮助页面，了解有关适用法律法规和亚马逊政策的信息。
- 此电子邮件末尾的表格提供了特定于商品的合规性要求。
- 如何重新启售商品？
- 要提供所需的合规信息，请前往 账户状况 页面并找到商品合规性请求：
--
- 如果您有所需的文件，请按照相关说明提交您的合规文件。
--
- 如果您认为您的商品无需遵守这些要求，请提交相关文件，说明它们为何不受这些合规要求的约束。
- 有关分步操作说明，请参阅 提交合规文件或对文件请求提出申诉 帮助页面。
- 为避免进一步影响您的账户，请停售或删除您不打算销售或申诉的任何不合规商品。
- 如果我未执行上述操作，会怎么样？
- 如果您未在“账户状况”页面显示的截止日期之前提供所需的合规信息，我们可能会停售受影响的商品。
- 我们愿意随时为您提供帮助。
- 有关更多信息，请观看卖家大学中的 安全与合规简介 视频
- 如果您有其他问题，请在您的 账户状况 控制面板上提交请求。
- 亚马逊商品安全与合规性
- 受影响的商品
- 详情
- Roaxkois Töpferset für Kinder, Töpferset für Zuhause mit ton lufttrocknend, Töpferscheibe Elektrisch, Diamant Aufkleber, Kreativ Set für Kinder, Geschenk-Ideen, Geschenk für Mädchen Jungen
- ASIN： B0DL3PC2WS
- 亚马逊要求您证明自己在亚马逊德国站上架的儿童玩具符合适用的法律、法规、标准和亚马逊政策。
-要销售儿童玩具，您必须满足 儿童玩具帮助页面 上列出的要求，并与我们的合作伙伴第三方测试、检验和认证 (TIC) 服务提供商合作，验证您的商品符合这些要求。
-儿童玩具是指供14岁或以下儿童在学习或玩耍时使用的商品。
-亚马逊根据以下标准来确定商品是否为“儿童玩具”：
-商品包装上的年龄分级标明该玩具专供 14 岁或以下儿童使用。
-产品的包装、展示、促销或广告显示该产品适合 14 岁或以下儿童使用。
-消费者通常认为该商品供 14 岁或以下儿童使用。
-有关合规要求、如何与 TIC 服务提供商合作的更多信息，或者要观看有关本政策涵盖的儿童玩具的视频，请访问 儿童玩具帮助页面 。
- 报告此电子邮件的问题
- 如果您有任何问题，请访问: Seller Central
- 要更改您的电子邮件首选项，请访问： 通知首选项
- 2026 Amazon.com 旗下公司 保留所有权利
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 6 Mar 2026 20:15:57 +0000</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
-        <is>
-          <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
-        </is>
-      </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>96
- Dzień dobry Weihai EU,
- niektóre z Twoich ofert są zagrożone dezaktywacją z powodu niespełnienia obowiązków dotyczących zgodności wystawianych przez Ciebie produktów z wymogami. Poniżej znajdziesz szczegółowe informacje oraz dalsze instrukcje. Oferty produktów, których dotyczy problem, wskazano na końcu niniejszej wiadomości e-mail.
- Dlaczego tak się stało?
- Podjęliśmy to działanie, ponieważ w przypadku tych produktów nie dostarczono obowiązkowych informacji dotyczących zgodności z wymogami. Więcej informacji na temat mających zastosowanie przepisów ustawowych i wykonawczych oraz zasad Amazon znajdziesz na stronie Bezpieczeństwo i zgodność produktu z wymogami .
- Informacje na temat wymogów dotyczących zgodności dla poszczególnych produktów znajdziesz w tabeli na końcu tej wiadomości e-mail.
- Jak mogę ponownie aktywować oferty?
- Aby dostarczyć niezbędne informacje dotyczące zgodności z wymogami, przejdź do panelu Kondycja konta i znajdź żądania dotyczące zgodności produktu z wymogami:
--
- Jeśli dysponujesz wymaganymi dokumentami zgodności, postępuj zgodnie z instrukcjami, aby je przesłać.
--
- Jeśli uważasz, że Twoje produkty są zwolnione z wymogów dotyczących zgodności, prześlij d</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 6 Mar 2026 20:15:27 +0000</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F107" s="2" t="inlineStr">
-        <is>
-          <t>Dien productveiligheidsdocumentatie in om de deactivering van de
- productvermelding te voorkomen</t>
-        </is>
-      </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hallo Weihai EU,
- Enkele van je productvermeldingen lopen het risico op deactivering omdat er verplichte nalevingsvereisten voor je producten ontbreken. Bekijk de gegevens en de stappen hieronder. De betreffende productvermeldingen worden aan het einde van deze e-mail weergegeven.
- Waarom gebeurt dit?
- We hebben deze actie ondernomen omdat voor deze producten verplichte nalevingsinformatie ontbreekt. Raadpleeg onze hulp-pagina Productveiligheid en -conformiteit voor informatie over de toepasselijke wet- en regelgeving en het Amazon-beleid.
- De tabel aan het einde van deze e-mail bevat productspecifieke nalevingsvereisten.
- Hoe activeer ik mijn productvermeldingen opnieuw?
- Als je de vereiste nalevingsgegevens wilt verstrekken, ga je naar de pagina Accountstatus en zoek je de aanvragen voor productconformiteit:
--
- Als je over de vereiste documentatie beschikt, volg je de instructies om je nalevingsdocumenten in te dienen.
--
- Als je van mening bent dat je producten zijn vrijgesteld van deze vereisten, dien dan documentatie in waaruit blijkt wat de reden is dat ze niet aan deze nalevingsvereisten zijn onderworpen.
- Raadpleeg voor stapsgewijze instructies onze hulp-pagina Documente</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 6 Mar 2026 20:12:48 +0000</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
-        </is>
-      </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hej Weihai EU!
- Vissa av dina produktposter riskerar att inaktiveras på grund av att det saknas obligatorisk information om överensstämmelse för produkterna. Granska informationen och följande steg nedan. De berörda produktposterna visas i slutet av det här e-postmeddelandet.
- Varför händer det här?
- Vi vidtar den här åtgärden eftersom det saknas obligatorisk information om överensstämmelse för de här produkterna. Läs vår hjälpsida för Produktsäkerhet och -överensstämmelse för information om tillämpliga lagar, förordningar och Amazons policyer.
- Tabellen i slutet av detta e-postmeddelande innehåller produktspecifika krav för överensstämmelse.
- Hur återaktiverar jag mina produktposter?
- Om du vill tillhandahålla den begärda överensstämmelseinformationen går du till sidan Kontostatus och letar upp begäranden om produktöverensstämmelse:
--
- Om du har den obligatoriska dokumentationen ska du skicka in dina överensstämmelsedokument enligt instruktionerna.
--
- Om du tror att dina produkter är undantagna från dessa krav skickar du in dokumentation som visar varför de inte omfattas av dessa överensstämmelsekrav.
- Du hittar stegvisa instruktioner på vår hjälpsida om Skicka in intyg om öve</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 6 Mar 2026 20:07:18 +0000</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 2/2026</t>
-        </is>
-      </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
-        <is>
-          <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
-We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
-To access your invoice, go to your Seller Central Account &gt; Reports &gt; Tax Document Library &gt; Seller Fee Tax Invoices.
-In your Seller Central account, you will be able to view, download or print your invoice.
-If you have any questions, please contact Seller Support.
-Best regards,
-Amazon.co.uk</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 6 Mar 2026 20:02:17 +0000</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 2.2026</t>
-        </is>
-      </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
-Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
-Navigieren Sie in Ihrem Seller Central-Konto zu Berichte &gt; Steuerdokumente &gt; Rechnungen über Verkaufsgebühren, um auf Ihr Dokument (Rechnung) zuzugreifen.
-In Ihrem Seller Central-Konto können Sie Ihr Dokument (Rechnung) anzeigen, herunterladen oder ausdrucken.
-Wenden Sie sich bei weiteren Fragen bitte an die Verkäuferhilfe.
-Freundliche Grüße,
-Amazon.de</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 6 Mar 2026 20:02:06 +0000</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="inlineStr">
-        <is>
-          <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 2/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 2/2026)</t>
-        </is>
-      </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
-        <is>
-          <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
-We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
-Als je toegang wilt krijgen tot je factuur, ga je naar je Seller Central-account &gt; Overzichten &gt; Bibliotheek met belastingdocumenten &gt; Belastingfacturen voor kosten verkoper.
-In je Seller Central-account kun je je factuur bekijken, downloaden of afdrukken.
-Als je nog vragen hebt, kun je contact opnemen met de Ondersteuning voor verkopers.
-Met vriendelijke groeten,
-Amazon.com.be
- Monsieur/Madame Shen zhen shi wei hai zhong xin ke ji you xian,
-Nous vous écrivons pour vous informer que votre Facture Expédié Par Amazon pour le mois de 2/2026 est maintenant disponible dans votre compte Seller Central.
-Pour accéder à votre facture, rendez-vous sur votre compte Seller Central et veuillez accéder à la page Rapports &gt; Bibliothèque d'informations fiscales &gt; Factures des frais du vendeur.
-Dans votre compte Seller Central, vous pourrez afficher, télécharger ou imprimer votre facture.
-Pour toute question, contactez le Support Vendeur.
-Cordialement,
-Amazon.com.be</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 6 Mar 2026 19:35:00 +0000</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F112" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 2/2026</t>
-        </is>
-      </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
-        <is>
-          <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
-We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 2/2026 is now available in your Seller Central Account.
-To access your invoice, go to your Seller Central Account &gt; Reports &gt; Tax Document Library &gt; Seller Fee Tax Invoices.
-In your Seller Central account, you will be able to view, download or print your invoice.
-If you have any questions, please contact Seller Support.
-Best regards,
-Amazon.co.uk</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 6 Mar 2026 19:32:44 +0000</t>
-        </is>
-      </c>
-      <c r="E113" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F113" s="2" t="inlineStr">
-        <is>
-          <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
-        </is>
-      </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
-        <is>
-          <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
-Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
-Navigieren Sie in Ihrem Seller Central-Konto zu Berichte &gt; Steuerdokumente &gt; Rechnungen über Verkaufsgebühren, um auf Ihr Dokument (Rechnung) zuzugreifen.
-In Ihrem Seller Central-Konto können Sie Ihr Dokument (Rechnung) anzeigen, herunterladen oder ausdrucken.
-Wenden Sie sich bei weiteren Fragen bitte an die Verkäuferhilfe.
-Freundliche Grüße,
-Amazon.de</t>
-        </is>
-      </c>
-    </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>法务/侵权类</t>
+          <t>货件/库存类</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -6099,514 +6051,21 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Fri, 6 Mar 2026 19:24:20 +0000</t>
+          <t>Fri, 27 Mar 2026 09:57:24 +0000</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>donotreply@amazon.com</t>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>Je Factuur Verkoper Amazon.nl voor 2/2026</t>
+          <t>Create FBA removal order by 2026-04-09</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr"/>
       <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
-We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
-Als je toegang wilt krijgen tot je factuur, ga je naar je Seller Central-account &gt; Overzichten &gt; Bibliotheek met belastingdocumenten &gt; Belastingfacturen voor kosten verkoper.
-In je Seller Central-account kun je je factuur bekijken, downloaden of afdrukken.
-Als je nog vragen hebt, kun je contact opnemen met de Ondersteuning voor verkopers.
-Met vriendelijke groeten,
-Amazon.nl</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 6 Mar 2026 18:55:05 +0000</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
-        </is>
-      </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
-        <is>
-          <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
-Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
-Navigieren Sie in Ihrem Seller Central-Konto zu Berichte &gt; Steuerdokumente &gt; Rechnungen über Verkaufsgebühren, um auf Ihr Dokument (Rechnung) zuzugreifen.
-In Ihrem Seller Central-Konto können Sie Ihr Dokument (Rechnung) anzeigen, herunterladen oder ausdrucken.
-Wenden Sie sich bei weiteren Fragen bitte an die Verkäuferhilfe.
-Freundliche Grüße,
-Amazon.de</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 6 Mar 2026 18:24:37 +0000</t>
-        </is>
-      </c>
-      <c r="E116" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F116" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon.co.uk Merchant Invoice for 2/2026</t>
-        </is>
-      </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
-We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
-To access your invoice, go to your Seller Central Account &gt; Reports &gt; Tax Document Library &gt; Seller Fee Tax Invoices.
-In your Seller Central account, you will be able to view, download or print your invoice.
-If you have any questions, please contact Seller Support.
-Best regards,
-Amazon.co.uk</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 6 Mar 2026 17:58:56 +0000</t>
-        </is>
-      </c>
-      <c r="E117" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F117" s="2" t="inlineStr">
-        <is>
-          <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 2/2026</t>
-        </is>
-      </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
-        <is>
-          <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
-We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
-Als je toegang wilt krijgen tot je factuur, ga je naar je Seller Central-account &gt; Overzichten &gt; Bibliotheek met belastingdocumenten &gt; Belastingfacturen voor kosten verkoper.
-In je Seller Central-account kun je je factuur bekijken, downloaden of afdrukken.
-Als je nog vragen hebt, kun je contact opnemen met de Ondersteuning voor verkopers.
-Met vriendelijke groeten,
-Amazon.nl</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 6 Mar 2026 17:48:50 +0000</t>
-        </is>
-      </c>
-      <c r="E118" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F118" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon.ie Merchant Invoice for 2/2026</t>
-        </is>
-      </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
-        <is>
-          <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
-We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
-To access your invoice, go to your Seller Central Account &gt; Reports &gt; Tax Document Library &gt; Seller Fee Tax Invoices.
-In your Seller Central account, you will be able to view, download or print your invoice.
-If you have any questions, please contact Seller Support.
-Best regards,
-Amazon.ie</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 6 Mar 2026 17:11:22 +0000</t>
-        </is>
-      </c>
-      <c r="E119" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F119" s="2" t="inlineStr">
-        <is>
-          <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 2.2026</t>
-        </is>
-      </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
-        <is>
-          <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
-Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
-Navigieren Sie in Ihrem Seller Central-Konto zu Berichte &gt; Steuerdokumente &gt; Rechnungen über Verkaufsgebühren, um auf Ihr Dokument (Rechnung) zuzugreifen.
-In Ihrem Seller Central-Konto können Sie Ihr Dokument (Rechnung) anzeigen, herunterladen oder ausdrucken.
-Wenden Sie sich bei weiteren Fragen bitte an die Verkäuferhilfe.
-Freundliche Grüße,
-Amazon.de</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 6 Mar 2026 16:54:03 +0000</t>
-        </is>
-      </c>
-      <c r="E120" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F120" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 2/2026</t>
-        </is>
-      </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
-        <is>
-          <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
-We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
-To access your invoice, go to your Seller Central Account &gt; Reports &gt; Tax Document Library &gt; Seller Fee Tax Invoices.
-In your Seller Central account, you will be able to view, download or print your invoice.
-If you have any questions, please contact Seller Support.
-Best regards,
-Amazon.co.uk</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 6 Mar 2026 16:44:53 +0000</t>
-        </is>
-      </c>
-      <c r="E121" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F121" s="2" t="inlineStr">
-        <is>
-          <t>Je Factuur Verkoper Amazon.com.be voor 2/2026 (Votre Facture
- Vendeur Amazon.com.be pour le mois de 2/2026)</t>
-        </is>
-      </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
-        <is>
-          <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
-We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
-Als je toegang wilt krijgen tot je factuur, ga je naar je Seller Central-account &gt; Overzichten &gt; Bibliotheek met belastingdocumenten &gt; Belastingfacturen voor kosten verkoper.
-In je Seller Central-account kun je je factuur bekijken, downloaden of afdrukken.
-Als je nog vragen hebt, kun je contact opnemen met de Ondersteuning voor verkopers.
-Met vriendelijke groeten,
-Amazon.com.be
- Monsieur/Madame Shen zhen shi wei hai zhong xin ke ji you xian,
-Nous vous écrivons pour vous informer que votre Facture Vendeur pour le mois de 2/2026 est maintenant disponible dans votre compte Seller Central.
-Pour accéder à votre facture, rendez-vous sur votre compte Seller Central et veuillez accéder à la page Rapports &gt; Bibliothèque d'informations fiscales &gt; Factures des frais du vendeur.
-Dans votre compte Seller Central, vous pourrez afficher, télécharger ou imprimer votre facture.
-Pour toute question, contactez le Support Vendeur.
-Cordialement,
-Amazon.com.be</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 6 Mar 2026 16:38:12 +0000</t>
-        </is>
-      </c>
-      <c r="E122" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F122" s="2" t="inlineStr">
-        <is>
-          <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 2/2026</t>
-        </is>
-      </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
-We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
-Als je toegang wilt krijgen tot je factuur, ga je naar je Seller Central-account &gt; Overzichten &gt; Bibliotheek met belastingdocumenten &gt; Belastingfacturen voor kosten verkoper.
-In je Seller Central-account kun je je factuur bekijken, downloaden of afdrukken.
-Als je nog vragen hebt, kun je contact opnemen met de Ondersteuning voor verkopers.
-Met vriendelijke groeten,
-Amazon.nl</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 6 Mar 2026 16:28:10 +0000</t>
-        </is>
-      </c>
-      <c r="E123" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F123" s="2" t="inlineStr">
-        <is>
-          <t>La tua Fattura Elettronica Amazon Marketing Service Amazon.it per
- 2/2026</t>
-        </is>
-      </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
-        <is>
-          <t>Gentile Shen zhen shi wei hai zhong xin ke ji you xian,
-Ti informiamo che la tua Fattura Elettronica Amazon Marketing Service per il mese di 2/2026 è ora disponibile sul tuo account di Seller Central.
-Per visualizzare la tua fattura, vai sul tuo Account Seller Central &gt; Report &gt; Documentazione fiscale &gt; "Fatture delle commissioni addebitate al venditore".
-Dall’account Seller Central potrai visualizzare, scaricare o stampare la tua fattura.
-Per qualsiasi domanda, contatta il Support al venditore.
-Distinti saluti,
-Amazon.it</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 6 Mar 2026 16:09:11 +0000</t>
-        </is>
-      </c>
-      <c r="E124" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F124" s="2" t="inlineStr">
-        <is>
-          <t>Din Faktura Säljare Amazon.se för 2/2026</t>
-        </is>
-      </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
-        <is>
-          <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
-Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
-För att komma åt ditt fakturagår du till ditt Seller Central-konto &gt; Rapporter &gt; Bibliotek för skattedokument &gt; Skattefakturor för säljaravgifter.
-På ditt Seller Central-konto kan du se, ladda ner eller skriva ut ditt faktura.
-Om du har några frågor, kontakta säljarsupport.
-Vänliga hälsningar,
-Amazon.se</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 27 Mar 2026 09:57:24 +0000</t>
-        </is>
-      </c>
-      <c r="E125" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F125" s="2" t="inlineStr">
-        <is>
-          <t>Create FBA removal order by 2026-04-09</t>
-        </is>
-      </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -6627,39 +6086,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 09:55:39 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6682,39 +6141,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:45:50 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-02</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -6735,39 +6194,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:04:22 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6791,39 +6250,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 09:25:34 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6846,39 +6305,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 10:45:45 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -6901,39 +6360,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 10:21:22 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-03-26</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -6955,39 +6414,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 18:36:24 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -7003,39 +6462,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Sun, 22 Mar 2026 03:22:21 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -7051,40 +6510,40 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:33:36 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>[Action Required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7103,40 +6562,40 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:34:06 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>[Action required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7154,39 +6613,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 17:09:21 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Envie os documentos de conformidade do produto para evitar a remoção da oferta</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
  Envie os documentos de conformidade do produto para evitar a remoção da oferta
@@ -7200,39 +6659,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 12:07:27 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Atenda aos requisitos de conformidade em ofertas</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
 Ação necessária: Informações importantes sobre suas ofertas
@@ -7250,39 +6709,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 12:42:53 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.nl&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Wijziging in geschiktheid voor opties voor premiumverzending</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>96
 Wijziging in geschiktheid voor opties voor premiumverzending
